--- a/my/selfHardWarePCB/MotorDriver/采购元件/采购订单.xlsx
+++ b/my/selfHardWarePCB/MotorDriver/采购元件/采购订单.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\project\roboticArm\my\selfHardWarePCB\MotorDriver\采购元件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E38042F1-8B61-46D3-8FFF-BECDE6DC0636}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97ECD086-4D9B-4464-BF89-835196CD43BB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,9 +17,9 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="ExternalData_1" localSheetId="0" hidden="1">Sheet2!$A$1:$M$41</definedName>
+    <definedName name="ExternalData_1" localSheetId="0" hidden="1">Sheet2!$B$1:$N$44</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="166">
   <si>
     <t>Reference</t>
   </si>
@@ -517,13 +517,37 @@
   </si>
   <si>
     <t>SH1.0-2P</t>
+  </si>
+  <si>
+    <t>Motor-42电路板</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嘉立创</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Motor-20电路板</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>合计</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>序号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -538,16 +562,44 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="26"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor theme="9" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -555,17 +607,283 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="16">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -580,8 +898,8 @@
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_1" connectionId="1" xr16:uid="{11B00EDC-18EF-409A-B027-911367A871E6}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="14">
-    <queryTableFields count="13">
+  <queryTableRefresh nextId="15" unboundColumnsRight="1">
+    <queryTableFields count="14">
       <queryTableField id="1" name="Reference" tableColumnId="1"/>
       <queryTableField id="2" name="Qty" tableColumnId="2"/>
       <queryTableField id="3" name="Value" tableColumnId="3"/>
@@ -595,28 +913,30 @@
       <queryTableField id="11" name="总价" tableColumnId="11"/>
       <queryTableField id="12" name="列1" tableColumnId="12"/>
       <queryTableField id="13" name="列2" tableColumnId="13"/>
+      <queryTableField id="14" dataBound="0" tableColumnId="14"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D5284B6D-A3CA-4204-B294-9A9A627B1073}" name="Motor_42" displayName="Motor_42" ref="A1:M41" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:M41" xr:uid="{DDA92F07-1E27-4D0D-8E52-531C101C7A12}"/>
-  <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{1AE980A1-4BE5-4C5E-8F94-F7FD33714AC1}" uniqueName="1" name="Reference" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{AAF91CCE-B607-4529-861A-652BA4BCCCF6}" uniqueName="2" name="Qty" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{BA68C690-0835-4E3A-9638-221E47CABFE0}" uniqueName="3" name="Value" queryTableFieldId="3"/>
-    <tableColumn id="4" xr3:uid="{0825B3F4-332A-4D2F-93FB-4A20CCB5F8C0}" uniqueName="4" name="DNP" queryTableFieldId="4"/>
-    <tableColumn id="5" xr3:uid="{0E123BDA-5A1A-46BD-B11D-3A9FF0D66F63}" uniqueName="5" name="Exclude from BOM" queryTableFieldId="5"/>
-    <tableColumn id="6" xr3:uid="{E0D8AC31-372B-4CA0-AB11-EBA4C3F358B2}" uniqueName="6" name="Exclude from Board" queryTableFieldId="6"/>
-    <tableColumn id="7" xr3:uid="{E4A08C8D-F146-42A2-B9DB-19223FB0709F}" uniqueName="7" name="Footprint" queryTableFieldId="7"/>
-    <tableColumn id="8" xr3:uid="{60EF6A44-C257-4D04-887E-59533CF580A6}" uniqueName="8" name="Datasheet" queryTableFieldId="8"/>
-    <tableColumn id="9" xr3:uid="{BDD187FA-7949-4883-80FF-E85C18C638EA}" uniqueName="9" name="采购数量" queryTableFieldId="9"/>
-    <tableColumn id="10" xr3:uid="{06AF81DC-0776-40C6-B844-FB43EA0EDF3F}" uniqueName="10" name="单价" queryTableFieldId="10"/>
-    <tableColumn id="11" xr3:uid="{60317022-3129-4F8F-A75E-A2746E31F565}" uniqueName="11" name="总价" queryTableFieldId="11"/>
-    <tableColumn id="12" xr3:uid="{BDE8E224-9B78-49FD-95A4-2821884BA503}" uniqueName="12" name="列1" queryTableFieldId="12"/>
-    <tableColumn id="13" xr3:uid="{2D306C18-1293-4366-9831-869F11E17F24}" uniqueName="13" name="列2" queryTableFieldId="13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D5284B6D-A3CA-4204-B294-9A9A627B1073}" name="Motor_42" displayName="Motor_42" ref="B1:O44" tableType="queryTable" totalsRowShown="0" headerRowDxfId="2" dataDxfId="1">
+  <autoFilter ref="B1:O44" xr:uid="{DDA92F07-1E27-4D0D-8E52-531C101C7A12}"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{1AE980A1-4BE5-4C5E-8F94-F7FD33714AC1}" uniqueName="1" name="Reference" queryTableFieldId="1" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{AAF91CCE-B607-4529-861A-652BA4BCCCF6}" uniqueName="2" name="Qty" queryTableFieldId="2" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{BA68C690-0835-4E3A-9638-221E47CABFE0}" uniqueName="3" name="Value" queryTableFieldId="3" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{0825B3F4-332A-4D2F-93FB-4A20CCB5F8C0}" uniqueName="4" name="DNP" queryTableFieldId="4" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{0E123BDA-5A1A-46BD-B11D-3A9FF0D66F63}" uniqueName="5" name="Exclude from BOM" queryTableFieldId="5" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{E0D8AC31-372B-4CA0-AB11-EBA4C3F358B2}" uniqueName="6" name="Exclude from Board" queryTableFieldId="6" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{E4A08C8D-F146-42A2-B9DB-19223FB0709F}" uniqueName="7" name="Footprint" queryTableFieldId="7" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{60EF6A44-C257-4D04-887E-59533CF580A6}" uniqueName="8" name="Datasheet" queryTableFieldId="8" dataDxfId="8"/>
+    <tableColumn id="9" xr3:uid="{BDD187FA-7949-4883-80FF-E85C18C638EA}" uniqueName="9" name="采购数量" queryTableFieldId="9" dataDxfId="7"/>
+    <tableColumn id="10" xr3:uid="{06AF81DC-0776-40C6-B844-FB43EA0EDF3F}" uniqueName="10" name="单价" queryTableFieldId="10" dataDxfId="6"/>
+    <tableColumn id="11" xr3:uid="{60317022-3129-4F8F-A75E-A2746E31F565}" uniqueName="11" name="总价" queryTableFieldId="11" dataDxfId="5"/>
+    <tableColumn id="12" xr3:uid="{BDE8E224-9B78-49FD-95A4-2821884BA503}" uniqueName="12" name="列1" queryTableFieldId="12" dataDxfId="4"/>
+    <tableColumn id="13" xr3:uid="{2D306C18-1293-4366-9831-869F11E17F24}" uniqueName="13" name="列2" queryTableFieldId="13" dataDxfId="3"/>
+    <tableColumn id="14" xr3:uid="{FFD1B69F-7395-44DC-9A79-76AD31871D16}" uniqueName="14" name="状态" queryTableFieldId="14" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -885,1706 +1205,1997 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A38F492-0FA3-4A98-BE1D-72E30BF86FD9}">
-  <dimension ref="A1:M41"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:O44"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="49.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.58203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.08203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.58203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.58203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.9140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="80.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="26.08203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.9140625" customWidth="1"/>
+    <col min="5" max="5" width="7.08203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.58203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.9140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="80.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="26.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="O1" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B2">
+      <c r="C2" s="2">
         <v>120</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2">
+      <c r="I2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="2">
         <v>100</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="2">
         <v>2.3E-2</v>
       </c>
-      <c r="K2">
+      <c r="L2" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
         <v>2.2999999999999998</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="O2" s="4"/>
+    </row>
+    <row r="3" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B3">
+      <c r="C3" s="2">
         <v>56</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="E3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3">
+      <c r="I3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="2">
         <v>100</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="2">
         <v>0.05</v>
       </c>
-      <c r="K3">
+      <c r="L3" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
         <v>5</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="O3" s="4"/>
+    </row>
+    <row r="4" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B4">
+      <c r="C4" s="2">
         <v>32</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="E4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4">
+      <c r="I4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="2">
         <v>40</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="2">
         <v>0.55000000000000004</v>
       </c>
-      <c r="K4">
+      <c r="L4" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
         <v>22</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="O4" s="4"/>
+    </row>
+    <row r="5" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B5">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="E5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I5">
+      <c r="I5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="2">
         <v>100</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="2">
         <v>1.9E-2</v>
       </c>
-      <c r="K5">
+      <c r="L5" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
         <v>1.9</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="O5" s="4"/>
+    </row>
+    <row r="6" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B6">
-        <v>8</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="E6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6">
+      <c r="I6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" s="2">
         <v>100</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="2">
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="K6">
+      <c r="L6" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
         <v>3.2</v>
       </c>
-      <c r="L6" t="s">
+      <c r="M6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="M6" t="s">
+      <c r="N6" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="O6" s="4"/>
+    </row>
+    <row r="7" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B7">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="C7" s="2">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="E7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7">
+      <c r="I7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" s="2">
         <v>100</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="2">
         <v>1.9E-2</v>
       </c>
-      <c r="K7">
+      <c r="L7" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
         <v>1.9</v>
       </c>
-      <c r="L7" t="s">
+      <c r="M7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="M7" t="s">
+      <c r="N7" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="O7" s="4"/>
+    </row>
+    <row r="8" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B8">
-        <v>8</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" t="s">
+      <c r="E8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8">
+      <c r="I8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" s="2">
         <v>100</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="2">
         <v>0.04</v>
       </c>
-      <c r="K8">
+      <c r="L8" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
         <v>4</v>
       </c>
-      <c r="L8" t="s">
+      <c r="M8" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="M8" t="s">
+      <c r="N8" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="O8" s="4"/>
+    </row>
+    <row r="9" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B9">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="C9" s="2">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" t="s">
+      <c r="E9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9">
+      <c r="I9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" s="2">
         <v>20</v>
       </c>
-      <c r="J9">
+      <c r="K9" s="2">
         <v>0.1</v>
       </c>
-      <c r="K9">
+      <c r="L9" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
         <v>2</v>
       </c>
-      <c r="L9" t="s">
-        <v>15</v>
-      </c>
-      <c r="M9" t="s">
+      <c r="M9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N9" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="O9" s="4"/>
+    </row>
+    <row r="10" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B10">
-        <v>8</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="C10" s="2">
+        <v>8</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="E10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I10">
+      <c r="I10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J10" s="2">
         <v>20</v>
       </c>
-      <c r="J10">
+      <c r="K10" s="2">
         <v>0.2</v>
       </c>
-      <c r="K10">
+      <c r="L10" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
         <v>4</v>
       </c>
-      <c r="L10" t="s">
+      <c r="M10" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="M10" t="s">
+      <c r="N10" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="O10" s="4"/>
+    </row>
+    <row r="11" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B11">
+      <c r="C11" s="2">
         <v>16</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="E11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H11" t="s">
-        <v>15</v>
-      </c>
-      <c r="I11">
+      <c r="I11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J11" s="2">
         <v>50</v>
       </c>
-      <c r="J11">
+      <c r="K11" s="2">
         <v>0.08</v>
       </c>
-      <c r="K11">
+      <c r="L11" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
         <v>4</v>
       </c>
-      <c r="L11" t="s">
+      <c r="M11" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="M11" t="s">
+      <c r="N11" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="O11" s="4"/>
+    </row>
+    <row r="12" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B12">
-        <v>8</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="C12" s="2">
+        <v>8</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12" t="s">
+      <c r="E12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I12">
+      <c r="I12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" s="2">
         <v>100</v>
       </c>
-      <c r="J12">
+      <c r="K12" s="2">
         <v>0.02</v>
       </c>
-      <c r="K12">
+      <c r="L12" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
         <v>2</v>
       </c>
-      <c r="L12" t="s">
+      <c r="M12" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="M12" t="s">
+      <c r="N12" s="2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="O12" s="4"/>
+    </row>
+    <row r="13" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B13">
-        <v>8</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="C13" s="2">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E13" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" t="s">
+      <c r="E13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="H13" t="s">
-        <v>15</v>
-      </c>
-      <c r="I13">
+      <c r="I13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J13" s="2">
         <v>16</v>
       </c>
-      <c r="J13">
+      <c r="K13" s="2">
         <v>0</v>
       </c>
-      <c r="K13">
+      <c r="L13" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
         <v>0</v>
       </c>
-      <c r="L13" t="s">
-        <v>15</v>
-      </c>
-      <c r="M13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="M13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O13" s="4"/>
+    </row>
+    <row r="14" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B14">
+      <c r="C14" s="2">
         <v>16</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14" t="s">
+      <c r="E14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="H14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I14">
+      <c r="I14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J14" s="2">
         <v>100</v>
       </c>
-      <c r="J14">
+      <c r="K14" s="2">
         <v>0.13370000000000001</v>
       </c>
-      <c r="K14">
-        <v>13.37</v>
-      </c>
-      <c r="L14" t="s">
+      <c r="L14" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
+        <v>13.370000000000001</v>
+      </c>
+      <c r="M14" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="M14" t="s">
+      <c r="N14" s="2" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="O14" s="4"/>
+    </row>
+    <row r="15" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B15">
-        <v>8</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="C15" s="2">
+        <v>8</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D15" t="s">
-        <v>15</v>
-      </c>
-      <c r="E15" t="s">
-        <v>15</v>
-      </c>
-      <c r="F15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15" t="s">
+      <c r="E15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="H15" t="s">
-        <v>15</v>
-      </c>
-      <c r="I15">
+      <c r="I15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J15" s="2">
         <v>10</v>
       </c>
-      <c r="J15">
+      <c r="K15" s="2">
         <v>0.20399999999999999</v>
       </c>
-      <c r="K15">
+      <c r="L15" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
         <v>2.04</v>
       </c>
-      <c r="L15" t="s">
+      <c r="M15" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="M15" t="s">
+      <c r="N15" s="2" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="O15" s="4"/>
+    </row>
+    <row r="16" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B16">
-        <v>8</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="C16" s="2">
+        <v>8</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D16" t="s">
-        <v>15</v>
-      </c>
-      <c r="E16" t="s">
-        <v>15</v>
-      </c>
-      <c r="F16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G16" t="s">
+      <c r="E16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="H16" t="s">
-        <v>15</v>
-      </c>
-      <c r="I16">
+      <c r="I16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J16" s="2">
         <v>20</v>
       </c>
-      <c r="J16">
+      <c r="K16" s="2">
         <v>0.4</v>
       </c>
-      <c r="K16">
-        <v>8</v>
-      </c>
-      <c r="L16" t="s">
+      <c r="L16" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
+        <v>8</v>
+      </c>
+      <c r="M16" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="M16" t="s">
+      <c r="N16" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="O16" s="4"/>
+    </row>
+    <row r="17" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B17">
-        <v>8</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="C17" s="2">
+        <v>8</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D17" t="s">
-        <v>15</v>
-      </c>
-      <c r="E17" t="s">
-        <v>15</v>
-      </c>
-      <c r="F17" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17" t="s">
+      <c r="E17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H17" t="s">
-        <v>15</v>
-      </c>
-      <c r="I17">
+      <c r="I17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J17" s="2">
         <v>30</v>
       </c>
-      <c r="J17">
+      <c r="K17" s="2">
         <v>0.06</v>
       </c>
-      <c r="K17">
-        <v>1.8</v>
-      </c>
-      <c r="L17" t="s">
+      <c r="L17" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
+        <v>1.7999999999999998</v>
+      </c>
+      <c r="M17" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="M17" t="s">
+      <c r="N17" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="O17" s="4"/>
+    </row>
+    <row r="18" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B18">
+      <c r="C18" s="2">
         <v>24</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D18" t="s">
-        <v>15</v>
-      </c>
-      <c r="E18" t="s">
-        <v>15</v>
-      </c>
-      <c r="F18" t="s">
-        <v>15</v>
-      </c>
-      <c r="G18" t="s">
+      <c r="E18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="H18" t="s">
-        <v>15</v>
-      </c>
-      <c r="I18">
+      <c r="I18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J18" s="2">
         <v>30</v>
       </c>
-      <c r="J18">
+      <c r="K18" s="2">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="K18">
+      <c r="L18" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
         <v>2.1</v>
       </c>
-      <c r="L18" t="s">
+      <c r="M18" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="M18" t="s">
+      <c r="N18" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="O18" s="4"/>
+    </row>
+    <row r="19" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B19">
-        <v>8</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="C19" s="2">
+        <v>8</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D19" t="s">
-        <v>15</v>
-      </c>
-      <c r="E19" t="s">
-        <v>15</v>
-      </c>
-      <c r="F19" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19" t="s">
+      <c r="E19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="H19" t="s">
-        <v>15</v>
-      </c>
-      <c r="I19">
+      <c r="I19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J19" s="2">
         <v>30</v>
       </c>
-      <c r="J19">
+      <c r="K19" s="2">
         <v>0.04</v>
       </c>
-      <c r="K19">
+      <c r="L19" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
         <v>1.2</v>
       </c>
-      <c r="L19" t="s">
+      <c r="M19" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="M19" t="s">
+      <c r="N19" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="O19" s="4"/>
+    </row>
+    <row r="20" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B20">
+      <c r="C20" s="2">
         <v>40</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D20" t="s">
-        <v>15</v>
-      </c>
-      <c r="E20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F20" t="s">
-        <v>15</v>
-      </c>
-      <c r="G20" t="s">
+      <c r="E20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="H20" t="s">
-        <v>15</v>
-      </c>
-      <c r="I20">
+      <c r="I20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J20" s="2">
         <v>40</v>
       </c>
-      <c r="J20">
+      <c r="K20" s="2">
         <v>0.16</v>
       </c>
-      <c r="K20">
+      <c r="L20" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
         <v>6.4</v>
       </c>
-      <c r="L20" t="s">
+      <c r="M20" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="M20" t="s">
+      <c r="N20" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="O20" s="4"/>
+    </row>
+    <row r="21" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B21">
+      <c r="C21" s="2">
         <v>16</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D21" t="s">
-        <v>15</v>
-      </c>
-      <c r="E21" t="s">
-        <v>15</v>
-      </c>
-      <c r="F21" t="s">
-        <v>15</v>
-      </c>
-      <c r="G21" t="s">
+      <c r="E21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="H21" t="s">
-        <v>15</v>
-      </c>
-      <c r="I21">
+      <c r="I21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J21" s="2">
         <v>50</v>
       </c>
-      <c r="J21">
+      <c r="K21" s="2">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="K21">
-        <v>2.8</v>
-      </c>
-      <c r="L21" t="s">
+      <c r="L21" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
+        <v>2.8000000000000003</v>
+      </c>
+      <c r="M21" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="M21" t="s">
+      <c r="N21" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="O21" s="4"/>
+    </row>
+    <row r="22" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B22">
-        <v>8</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="C22" s="2">
+        <v>8</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D22" t="s">
-        <v>15</v>
-      </c>
-      <c r="E22" t="s">
-        <v>15</v>
-      </c>
-      <c r="F22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G22" t="s">
+      <c r="E22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="H22" t="s">
-        <v>15</v>
-      </c>
-      <c r="I22">
+      <c r="I22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J22" s="2">
         <v>50</v>
       </c>
-      <c r="J22">
+      <c r="K22" s="2">
         <v>0.09</v>
       </c>
-      <c r="K22">
+      <c r="L22" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
         <v>4.5</v>
       </c>
-      <c r="L22" t="s">
+      <c r="M22" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="M22" t="s">
+      <c r="N22" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="O22" s="4"/>
+    </row>
+    <row r="23" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B23">
-        <v>8</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="C23" s="2">
+        <v>8</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D23" t="s">
-        <v>15</v>
-      </c>
-      <c r="E23" t="s">
-        <v>15</v>
-      </c>
-      <c r="F23" t="s">
-        <v>15</v>
-      </c>
-      <c r="G23" t="s">
+      <c r="E23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="H23" t="s">
-        <v>15</v>
-      </c>
-      <c r="I23">
+      <c r="I23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J23" s="2">
         <v>100</v>
       </c>
-      <c r="J23">
+      <c r="K23" s="2">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="K23">
+      <c r="L23" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
         <v>1.5</v>
       </c>
-      <c r="L23" t="s">
+      <c r="M23" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="M23" t="s">
+      <c r="N23" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="O23" s="4"/>
+    </row>
+    <row r="24" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B24">
+      <c r="C24" s="2">
         <v>32</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D24" t="s">
-        <v>15</v>
-      </c>
-      <c r="E24" t="s">
-        <v>15</v>
-      </c>
-      <c r="F24" t="s">
-        <v>15</v>
-      </c>
-      <c r="G24" t="s">
+      <c r="E24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="H24" t="s">
-        <v>15</v>
-      </c>
-      <c r="I24">
+      <c r="I24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J24" s="2">
         <v>100</v>
       </c>
-      <c r="J24">
+      <c r="K24" s="2">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="K24">
+      <c r="L24" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
         <v>1.5</v>
       </c>
-      <c r="L24" t="s">
+      <c r="M24" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="M24" t="s">
+      <c r="N24" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="O24" s="4"/>
+    </row>
+    <row r="25" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B25">
+      <c r="C25" s="2">
         <v>16</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E25" t="s">
-        <v>15</v>
-      </c>
-      <c r="F25" t="s">
-        <v>15</v>
-      </c>
-      <c r="G25" t="s">
+      <c r="E25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="H25" t="s">
-        <v>15</v>
-      </c>
-      <c r="I25">
+      <c r="I25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J25" s="2">
         <v>100</v>
       </c>
-      <c r="J25">
+      <c r="K25" s="2">
         <v>0.02</v>
       </c>
-      <c r="K25">
+      <c r="L25" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
         <v>2</v>
       </c>
-      <c r="L25" t="s">
+      <c r="M25" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="M25" t="s">
+      <c r="N25" s="2" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="O25" s="4"/>
+    </row>
+    <row r="26" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B26">
-        <v>8</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="C26" s="2">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E26" t="s">
-        <v>15</v>
-      </c>
-      <c r="F26" t="s">
-        <v>15</v>
-      </c>
-      <c r="G26" t="s">
+      <c r="E26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="H26" t="s">
-        <v>15</v>
-      </c>
-      <c r="I26">
+      <c r="I26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J26" s="2">
         <v>100</v>
       </c>
-      <c r="J26">
+      <c r="K26" s="2">
         <v>0.06</v>
       </c>
-      <c r="K26">
+      <c r="L26" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
         <v>6</v>
       </c>
-      <c r="L26" t="s">
+      <c r="M26" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="M26" t="s">
+      <c r="N26" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="O26" s="4"/>
+    </row>
+    <row r="27" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B27">
-        <v>8</v>
-      </c>
-      <c r="C27" t="s">
+      <c r="C27" s="2">
+        <v>8</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D27" t="s">
-        <v>15</v>
-      </c>
-      <c r="E27" t="s">
-        <v>15</v>
-      </c>
-      <c r="F27" t="s">
-        <v>15</v>
-      </c>
-      <c r="G27" t="s">
+      <c r="E27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="H27" t="s">
-        <v>15</v>
-      </c>
-      <c r="I27">
+      <c r="I27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J27" s="2">
         <v>20</v>
       </c>
-      <c r="J27">
+      <c r="K27" s="2">
         <v>0.16</v>
       </c>
-      <c r="K27">
+      <c r="L27" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
         <v>3.2</v>
       </c>
-      <c r="L27" t="s">
+      <c r="M27" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="M27" t="s">
+      <c r="N27" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="O27" s="4"/>
+    </row>
+    <row r="28" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B28">
-        <v>8</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="C28" s="2">
+        <v>8</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D28" t="s">
-        <v>15</v>
-      </c>
-      <c r="E28" t="s">
-        <v>15</v>
-      </c>
-      <c r="F28" t="s">
-        <v>15</v>
-      </c>
-      <c r="G28" t="s">
+      <c r="E28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="H28" t="s">
-        <v>15</v>
-      </c>
-      <c r="I28">
+      <c r="I28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J28" s="2">
         <v>16</v>
       </c>
-      <c r="J28">
+      <c r="K28" s="2">
         <v>0.25</v>
       </c>
-      <c r="K28">
+      <c r="L28" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
         <v>4</v>
       </c>
-      <c r="L28" t="s">
+      <c r="M28" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="M28" t="s">
+      <c r="N28" s="2" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="O28" s="4"/>
+    </row>
+    <row r="29" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B29">
-        <v>8</v>
-      </c>
-      <c r="C29" t="s">
+      <c r="C29" s="2">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D29" t="s">
-        <v>15</v>
-      </c>
-      <c r="E29" t="s">
-        <v>15</v>
-      </c>
-      <c r="F29" t="s">
-        <v>15</v>
-      </c>
-      <c r="G29" t="s">
+      <c r="E29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="H29" t="s">
-        <v>15</v>
-      </c>
-      <c r="I29">
+      <c r="I29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J29" s="2">
         <v>100</v>
       </c>
-      <c r="J29">
+      <c r="K29" s="2">
         <v>0.02</v>
       </c>
-      <c r="K29">
+      <c r="L29" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
         <v>2</v>
       </c>
-      <c r="L29" t="s">
+      <c r="M29" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="M29" t="s">
+      <c r="N29" s="2" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+      <c r="O29" s="4"/>
+    </row>
+    <row r="30" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B30">
-        <v>8</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="C30" s="2">
+        <v>8</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D30" t="s">
-        <v>15</v>
-      </c>
-      <c r="E30" t="s">
-        <v>15</v>
-      </c>
-      <c r="F30" t="s">
-        <v>15</v>
-      </c>
-      <c r="G30" t="s">
+      <c r="E30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="H30" t="s">
-        <v>15</v>
-      </c>
-      <c r="I30">
+      <c r="I30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J30" s="2">
         <v>100</v>
       </c>
-      <c r="J30">
+      <c r="K30" s="2">
         <v>0.02</v>
       </c>
-      <c r="K30">
+      <c r="L30" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
         <v>2</v>
       </c>
-      <c r="L30" t="s">
+      <c r="M30" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="M30" t="s">
+      <c r="N30" s="2" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="O30" s="4"/>
+    </row>
+    <row r="31" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B31">
+      <c r="C31" s="2">
         <v>16</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="D31" t="s">
-        <v>15</v>
-      </c>
-      <c r="E31" t="s">
-        <v>15</v>
-      </c>
-      <c r="F31" t="s">
-        <v>15</v>
-      </c>
-      <c r="G31" t="s">
+      <c r="E31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="H31" t="s">
-        <v>15</v>
-      </c>
-      <c r="I31">
+      <c r="I31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J31" s="2">
         <v>50</v>
       </c>
-      <c r="J31">
+      <c r="K31" s="2">
         <v>8.7999999999999995E-2</v>
       </c>
-      <c r="K31">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="L31" t="s">
+      <c r="L31" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
+        <v>4.3999999999999995</v>
+      </c>
+      <c r="M31" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="M31" t="s">
+      <c r="N31" s="2" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="O31" s="4"/>
+    </row>
+    <row r="32" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B32">
+      <c r="C32" s="2">
         <v>16</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D32" t="s">
-        <v>15</v>
-      </c>
-      <c r="E32" t="s">
-        <v>15</v>
-      </c>
-      <c r="F32" t="s">
-        <v>15</v>
-      </c>
-      <c r="G32" t="s">
+      <c r="E32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H32" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="H32" t="s">
-        <v>15</v>
-      </c>
-      <c r="I32">
+      <c r="I32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J32" s="2">
         <v>20</v>
       </c>
-      <c r="J32">
+      <c r="K32" s="2">
         <v>1.45</v>
       </c>
-      <c r="K32">
+      <c r="L32" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
         <v>29</v>
       </c>
-      <c r="L32" t="s">
+      <c r="M32" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="M32" t="s">
+      <c r="N32" s="2" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+      <c r="O32" s="4"/>
+    </row>
+    <row r="33" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B33">
-        <v>8</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="C33" s="2">
+        <v>8</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="D33" t="s">
-        <v>15</v>
-      </c>
-      <c r="E33" t="s">
-        <v>15</v>
-      </c>
-      <c r="F33" t="s">
-        <v>15</v>
-      </c>
-      <c r="G33" t="s">
+      <c r="E33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H33" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="H33" t="s">
-        <v>15</v>
-      </c>
-      <c r="I33">
-        <v>8</v>
-      </c>
-      <c r="J33">
+      <c r="I33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J33" s="2">
+        <v>8</v>
+      </c>
+      <c r="K33" s="2">
         <v>4.45</v>
       </c>
-      <c r="K33">
+      <c r="L33" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
         <v>35.6</v>
       </c>
-      <c r="L33" t="s">
+      <c r="M33" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="M33" t="s">
+      <c r="N33" s="2" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+      <c r="O33" s="4"/>
+    </row>
+    <row r="34" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B34">
-        <v>8</v>
-      </c>
-      <c r="C34" t="s">
+      <c r="C34" s="2">
+        <v>8</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="D34" t="s">
-        <v>15</v>
-      </c>
-      <c r="E34" t="s">
-        <v>15</v>
-      </c>
-      <c r="F34" t="s">
-        <v>15</v>
-      </c>
-      <c r="G34" t="s">
+      <c r="E34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H34" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="H34" t="s">
-        <v>15</v>
-      </c>
-      <c r="I34">
+      <c r="I34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J34" s="2">
         <v>20</v>
       </c>
-      <c r="J34">
+      <c r="K34" s="2">
         <v>0.88</v>
       </c>
-      <c r="K34">
+      <c r="L34" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
         <v>17.600000000000001</v>
       </c>
-      <c r="L34" t="s">
+      <c r="M34" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="M34" t="s">
+      <c r="N34" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+      <c r="O34" s="4"/>
+    </row>
+    <row r="35" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B35">
-        <v>8</v>
-      </c>
-      <c r="C35" t="s">
+      <c r="C35" s="2">
+        <v>8</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="D35" t="s">
-        <v>15</v>
-      </c>
-      <c r="E35" t="s">
-        <v>15</v>
-      </c>
-      <c r="F35" t="s">
-        <v>15</v>
-      </c>
-      <c r="G35" t="s">
+      <c r="E35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H35" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="H35" t="s">
-        <v>15</v>
-      </c>
-      <c r="I35">
+      <c r="I35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J35" s="2">
         <v>10</v>
       </c>
-      <c r="J35">
+      <c r="K35" s="2">
         <v>2</v>
       </c>
-      <c r="K35">
+      <c r="L35" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
         <v>20</v>
       </c>
-      <c r="L35" t="s">
+      <c r="M35" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="M35" t="s">
+      <c r="N35" s="2" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+      <c r="O35" s="4"/>
+    </row>
+    <row r="36" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B36">
-        <v>8</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="C36" s="2">
+        <v>8</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="D36" t="s">
-        <v>15</v>
-      </c>
-      <c r="E36" t="s">
-        <v>15</v>
-      </c>
-      <c r="F36" t="s">
-        <v>15</v>
-      </c>
-      <c r="G36" t="s">
+      <c r="E36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="H36" t="s">
-        <v>15</v>
-      </c>
-      <c r="I36">
+      <c r="I36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J36" s="2">
         <v>20</v>
       </c>
-      <c r="J36">
+      <c r="K36" s="2">
         <v>0.49</v>
       </c>
-      <c r="K36">
+      <c r="L36" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
         <v>9.8000000000000007</v>
       </c>
-      <c r="L36" t="s">
+      <c r="M36" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="M36" t="s">
+      <c r="N36" s="2" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+      <c r="O36" s="4"/>
+    </row>
+    <row r="37" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B37">
-        <v>8</v>
-      </c>
-      <c r="C37" t="s">
+      <c r="C37" s="2">
+        <v>8</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="D37" t="s">
-        <v>15</v>
-      </c>
-      <c r="E37" t="s">
-        <v>15</v>
-      </c>
-      <c r="F37" t="s">
-        <v>15</v>
-      </c>
-      <c r="G37" t="s">
+      <c r="E37" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H37" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="H37" t="s">
-        <v>15</v>
-      </c>
-      <c r="I37">
-        <v>8</v>
-      </c>
-      <c r="J37">
+      <c r="I37" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J37" s="2">
+        <v>8</v>
+      </c>
+      <c r="K37" s="2">
         <v>3.9</v>
       </c>
-      <c r="K37">
+      <c r="L37" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
         <v>31.2</v>
       </c>
-      <c r="L37" t="s">
+      <c r="M37" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="M37" t="s">
+      <c r="N37" s="2" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+      <c r="O37" s="4"/>
+    </row>
+    <row r="38" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="B38">
-        <v>8</v>
-      </c>
-      <c r="C38" t="s">
+      <c r="C38" s="2">
+        <v>8</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E38" t="s">
-        <v>15</v>
-      </c>
-      <c r="F38" t="s">
-        <v>15</v>
-      </c>
-      <c r="G38" t="s">
+      <c r="E38" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H38" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="H38" t="s">
-        <v>15</v>
-      </c>
-      <c r="I38">
-        <v>8</v>
-      </c>
-      <c r="J38">
+      <c r="I38" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J38" s="2">
+        <v>8</v>
+      </c>
+      <c r="K38" s="2">
         <v>3.76</v>
       </c>
-      <c r="K38">
+      <c r="L38" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
         <v>30.08</v>
       </c>
-      <c r="L38" t="s">
+      <c r="M38" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="M38" t="s">
+      <c r="N38" s="2" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+      <c r="O38" s="4"/>
+    </row>
+    <row r="39" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="3">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B39">
-        <v>8</v>
-      </c>
-      <c r="C39" t="s">
+      <c r="C39" s="2">
+        <v>8</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="D39" t="s">
-        <v>15</v>
-      </c>
-      <c r="E39" t="s">
-        <v>15</v>
-      </c>
-      <c r="F39" t="s">
-        <v>15</v>
-      </c>
-      <c r="G39" t="s">
+      <c r="E39" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H39" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="H39" t="s">
-        <v>15</v>
-      </c>
-      <c r="I39">
-        <v>8</v>
-      </c>
-      <c r="J39">
+      <c r="I39" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J39" s="2">
+        <v>8</v>
+      </c>
+      <c r="K39" s="2">
         <v>3.5</v>
       </c>
-      <c r="K39">
+      <c r="L39" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
         <v>28</v>
       </c>
-      <c r="L39" t="s">
+      <c r="M39" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="M39" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+      <c r="N39" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O39" s="4"/>
+    </row>
+    <row r="40" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B40">
-        <v>8</v>
-      </c>
-      <c r="C40" t="s">
+      <c r="C40" s="2">
+        <v>8</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D40" t="s">
-        <v>15</v>
-      </c>
-      <c r="E40" t="s">
-        <v>15</v>
-      </c>
-      <c r="F40" t="s">
-        <v>15</v>
-      </c>
-      <c r="G40" t="s">
+      <c r="E40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H40" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="H40" t="s">
-        <v>15</v>
-      </c>
-      <c r="I40">
+      <c r="I40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J40" s="2">
         <v>10</v>
       </c>
-      <c r="J40">
+      <c r="K40" s="2">
         <v>0.68</v>
       </c>
-      <c r="K40">
-        <v>6.8</v>
-      </c>
-      <c r="L40" t="s">
+      <c r="L40" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
+        <v>6.8000000000000007</v>
+      </c>
+      <c r="M40" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="M40" t="s">
+      <c r="N40" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>15</v>
-      </c>
-      <c r="C41" t="s">
+      <c r="O40" s="4"/>
+    </row>
+    <row r="41" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="3">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D41" t="s">
-        <v>15</v>
-      </c>
-      <c r="E41" t="s">
-        <v>15</v>
-      </c>
-      <c r="F41" t="s">
-        <v>15</v>
-      </c>
-      <c r="G41" t="s">
-        <v>15</v>
-      </c>
-      <c r="H41" t="s">
-        <v>15</v>
-      </c>
-      <c r="I41">
+      <c r="E41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J41" s="2">
         <v>20</v>
       </c>
-      <c r="J41">
+      <c r="K41" s="2">
         <v>0.02</v>
       </c>
-      <c r="K41">
+      <c r="L41" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
         <v>0.4</v>
       </c>
-      <c r="L41" t="s">
-        <v>15</v>
-      </c>
-      <c r="M41" t="s">
-        <v>15</v>
-      </c>
+      <c r="M41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O41" s="4"/>
+    </row>
+    <row r="42" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2">
+        <v>10</v>
+      </c>
+      <c r="K42" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="L42" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
+        <v>55</v>
+      </c>
+      <c r="M42" s="2"/>
+      <c r="N42" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="O42" s="4"/>
+    </row>
+    <row r="43" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="3">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2">
+        <v>5</v>
+      </c>
+      <c r="K43" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="L43" s="2">
+        <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
+        <v>27.5</v>
+      </c>
+      <c r="M43" s="2"/>
+      <c r="N43" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="O43" s="4"/>
+    </row>
+    <row r="44" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="L44" s="1">
+        <f>SUM(L2:L43)</f>
+        <v>412.09</v>
+      </c>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+      <c r="O44" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="26" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>

--- a/my/selfHardWarePCB/MotorDriver/采购元件/采购订单.xlsx
+++ b/my/selfHardWarePCB/MotorDriver/采购元件/采购订单.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\project\roboticArm\my\selfHardWarePCB\MotorDriver\采购元件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97ECD086-4D9B-4464-BF89-835196CD43BB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F53F56CD-72B5-4D68-BD03-80F553C784C4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="177">
   <si>
     <t>Reference</t>
   </si>
@@ -126,9 +126,6 @@
     <t>100pF</t>
   </si>
   <si>
-    <t>0402 100pF 50V NPO 5%</t>
-  </si>
-  <si>
     <t>C20</t>
   </si>
   <si>
@@ -174,9 +171,6 @@
     <t>D2</t>
   </si>
   <si>
-    <t>SMBJ28CA</t>
-  </si>
-  <si>
     <t>SMBJ-CA_MFG</t>
   </si>
   <si>
@@ -192,9 +186,6 @@
     <t>SOD-323</t>
   </si>
   <si>
-    <t>1N5819WS 0805 SOD-323</t>
-  </si>
-  <si>
     <t>D6</t>
   </si>
   <si>
@@ -240,9 +231,6 @@
     <t>IND-201612</t>
   </si>
   <si>
-    <t>YSMC201612H-6R8M8</t>
-  </si>
-  <si>
     <t>深圳市元易购买电子</t>
   </si>
   <si>
@@ -255,9 +243,6 @@
     <t>2520-L</t>
   </si>
   <si>
-    <t>LQM2HPN2R2MG0L 2520 2.2uH 1.3A</t>
-  </si>
-  <si>
     <t>P1</t>
   </si>
   <si>
@@ -288,9 +273,6 @@
     <t>RES_0402</t>
   </si>
   <si>
-    <t>0402 1K 0.1% 25ppm</t>
-  </si>
-  <si>
     <t>R3,R8</t>
   </si>
   <si>
@@ -306,9 +288,6 @@
     <t>R4</t>
   </si>
   <si>
-    <t>NCP15XH103F03RC</t>
-  </si>
-  <si>
     <t>NCP15XH103F03RC 10K 1%</t>
   </si>
   <si>
@@ -429,9 +408,6 @@
     <t>U4</t>
   </si>
   <si>
-    <t>TL431IDBZT</t>
-  </si>
-  <si>
     <t>SOT23-3</t>
   </si>
   <si>
@@ -439,9 +415,6 @@
   </si>
   <si>
     <t>U5</t>
-  </si>
-  <si>
-    <t>SN65HVD232D</t>
   </si>
   <si>
     <t>SO-8</t>
@@ -540,6 +513,212 @@
   </si>
   <si>
     <t>状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TL431IDBZT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NCP15XH103F03RC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>列3</t>
+  </si>
+  <si>
+    <t>SMBJ28CA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>列4</t>
+  </si>
+  <si>
+    <r>
+      <t>SMBJ28CA 是一款</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>‌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>600W 双向 TVS 二极管</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>‌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，主要用于电路防浪涌保护，工作电压 28V</t>
+    </r>
+  </si>
+  <si>
+    <t>LQM2HPN2R2MG0L 2520 2.2uH 1.3A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>电感</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0402 100pF 50V NPO 5%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0402 1K 0.1% 25ppm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1N5819WS 0805 SOD-323</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TL431IDBZT 是德州仪器 (Texas Instruments) 生产的一款 3 端可调精密分流稳压器电压基准芯片</t>
+  </si>
+  <si>
+    <t>没买1N5819W,买了两个1N5819WS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>NCP15XH103F03RC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> 是 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Murata</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>村田</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>）生产的一款 NTC 热敏电阻，主要用于</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>温度传感</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>和</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>补偿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>，核心参数包括 10kΩ 阻值、±1% 容差、0402 封装及 -40°C 至 125°C 工作温度范围。</t>
+    </r>
+  </si>
+  <si>
+    <t>TB67H450FNG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TB67H450FNG 是东芝生产的一款直流有刷电机驱动芯片</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SN65HVD232D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CAN总线收发器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>YSMC201612H-6R8M8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>功率电感</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -547,7 +726,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -584,8 +763,22 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -596,6 +789,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor theme="9" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -624,7 +823,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -638,11 +837,47 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="18">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -898,8 +1133,8 @@
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_1" connectionId="1" xr16:uid="{11B00EDC-18EF-409A-B027-911367A871E6}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="15" unboundColumnsRight="1">
-    <queryTableFields count="14">
+  <queryTableRefresh nextId="18" unboundColumnsRight="3">
+    <queryTableFields count="16">
       <queryTableField id="1" name="Reference" tableColumnId="1"/>
       <queryTableField id="2" name="Qty" tableColumnId="2"/>
       <queryTableField id="3" name="Value" tableColumnId="3"/>
@@ -914,15 +1149,17 @@
       <queryTableField id="12" name="列1" tableColumnId="12"/>
       <queryTableField id="13" name="列2" tableColumnId="13"/>
       <queryTableField id="14" dataBound="0" tableColumnId="14"/>
+      <queryTableField id="15" dataBound="0" tableColumnId="15"/>
+      <queryTableField id="16" dataBound="0" tableColumnId="16"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D5284B6D-A3CA-4204-B294-9A9A627B1073}" name="Motor_42" displayName="Motor_42" ref="B1:O44" tableType="queryTable" totalsRowShown="0" headerRowDxfId="2" dataDxfId="1">
-  <autoFilter ref="B1:O44" xr:uid="{DDA92F07-1E27-4D0D-8E52-531C101C7A12}"/>
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D5284B6D-A3CA-4204-B294-9A9A627B1073}" name="Motor_42" displayName="Motor_42" ref="B1:Q44" tableType="queryTable" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
+  <autoFilter ref="B1:Q44" xr:uid="{DDA92F07-1E27-4D0D-8E52-531C101C7A12}"/>
+  <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{1AE980A1-4BE5-4C5E-8F94-F7FD33714AC1}" uniqueName="1" name="Reference" queryTableFieldId="1" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{AAF91CCE-B607-4529-861A-652BA4BCCCF6}" uniqueName="2" name="Qty" queryTableFieldId="2" dataDxfId="14"/>
     <tableColumn id="3" xr3:uid="{BA68C690-0835-4E3A-9638-221E47CABFE0}" uniqueName="3" name="Value" queryTableFieldId="3" dataDxfId="13"/>
@@ -936,7 +1173,9 @@
     <tableColumn id="11" xr3:uid="{60317022-3129-4F8F-A75E-A2746E31F565}" uniqueName="11" name="总价" queryTableFieldId="11" dataDxfId="5"/>
     <tableColumn id="12" xr3:uid="{BDE8E224-9B78-49FD-95A4-2821884BA503}" uniqueName="12" name="列1" queryTableFieldId="12" dataDxfId="4"/>
     <tableColumn id="13" xr3:uid="{2D306C18-1293-4366-9831-869F11E17F24}" uniqueName="13" name="列2" queryTableFieldId="13" dataDxfId="3"/>
-    <tableColumn id="14" xr3:uid="{FFD1B69F-7395-44DC-9A79-76AD31871D16}" uniqueName="14" name="状态" queryTableFieldId="14" dataDxfId="0"/>
+    <tableColumn id="14" xr3:uid="{FFD1B69F-7395-44DC-9A79-76AD31871D16}" uniqueName="14" name="状态" queryTableFieldId="14" dataDxfId="2"/>
+    <tableColumn id="15" xr3:uid="{15C36A40-D5E1-413E-B5DE-DFE535402FD6}" uniqueName="15" name="列3" queryTableFieldId="15" dataDxfId="1"/>
+    <tableColumn id="16" xr3:uid="{A3C85DEF-07DA-406A-BAD4-CC7E1A7CC18B}" uniqueName="16" name="列4" queryTableFieldId="16" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1208,7 +1447,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O44"/>
+  <dimension ref="A1:Q44"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="49.1640625" bestFit="1" customWidth="1"/>
@@ -1224,11 +1463,14 @@
     <col min="12" max="12" width="13.25" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="80.6640625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="26.08203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="100.75" customWidth="1"/>
+    <col min="17" max="17" width="63.5" customWidth="1"/>
+    <col min="18" max="18" width="101" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1270,10 +1512,16 @@
         <v>12</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+        <v>156</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1317,9 +1565,13 @@
       <c r="N2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="O2" s="4"/>
-    </row>
-    <row r="3" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O2" s="4">
+        <v>1</v>
+      </c>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+    </row>
+    <row r="3" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1363,9 +1615,13 @@
       <c r="N3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="O3" s="4"/>
-    </row>
-    <row r="4" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O3" s="4">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+    </row>
+    <row r="4" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -1409,9 +1665,13 @@
       <c r="N4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="O4" s="4"/>
-    </row>
-    <row r="5" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O4" s="4">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+    </row>
+    <row r="5" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -1450,25 +1710,29 @@
         <v>1.9</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>29</v>
+        <v>165</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="O5" s="4"/>
-    </row>
-    <row r="6" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O5" s="4">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+    </row>
+    <row r="6" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C6" s="2">
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>15</v>
@@ -1496,25 +1760,29 @@
         <v>3.2</v>
       </c>
       <c r="M6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="N6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="N6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O6" s="4"/>
-    </row>
-    <row r="7" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O6" s="4">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+    </row>
+    <row r="7" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C7" s="2">
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>15</v>
@@ -1542,25 +1810,29 @@
         <v>1.9</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="O7" s="4"/>
-    </row>
-    <row r="8" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O7" s="4">
+        <v>1</v>
+      </c>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+    </row>
+    <row r="8" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C8" s="2">
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>15</v>
@@ -1588,37 +1860,41 @@
         <v>4</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="O8" s="4"/>
-    </row>
-    <row r="9" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O8" s="4">
+        <v>1</v>
+      </c>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+    </row>
+    <row r="9" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C9" s="2">
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>15</v>
@@ -1637,22 +1913,26 @@
         <v>15</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O9" s="4"/>
-    </row>
-    <row r="10" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+      <c r="O9" s="4">
+        <v>1</v>
+      </c>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+    </row>
+    <row r="10" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C10" s="2">
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>45</v>
+        <v>160</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>15</v>
@@ -1664,7 +1944,7 @@
         <v>15</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>15</v>
@@ -1680,71 +1960,80 @@
         <v>4</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="O10" s="4"/>
-    </row>
-    <row r="11" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O10" s="4">
+        <v>1</v>
+      </c>
+      <c r="P10" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="5">
+        <v>16</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="2">
-        <v>16</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H11" s="2" t="s">
+      <c r="I11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J11" s="5">
         <v>50</v>
       </c>
-      <c r="I11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" s="2">
-        <v>50</v>
-      </c>
-      <c r="K11" s="2">
+      <c r="K11" s="5">
         <v>0.08</v>
       </c>
-      <c r="L11" s="2">
+      <c r="L11" s="5">
         <f>Motor_42[[#This Row],[采购数量]]*Motor_42[[#This Row],[单价]]</f>
         <v>4</v>
       </c>
-      <c r="M11" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="N11" s="2" t="s">
+      <c r="M11" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="N11" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="O11" s="4"/>
-    </row>
-    <row r="12" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O11" s="6"/>
+      <c r="P11" s="6"/>
+      <c r="Q11" s="4" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C12" s="2">
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>15</v>
@@ -1756,7 +2045,7 @@
         <v>15</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>15</v>
@@ -1772,25 +2061,29 @@
         <v>2</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="O12" s="4"/>
-    </row>
-    <row r="13" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+      <c r="O12" s="4">
+        <v>1</v>
+      </c>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4"/>
+    </row>
+    <row r="13" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C13" s="2">
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>15</v>
@@ -1802,7 +2095,7 @@
         <v>15</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>15</v>
@@ -1824,19 +2117,21 @@
         <v>15</v>
       </c>
       <c r="O13" s="4"/>
-    </row>
-    <row r="14" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P13" s="4"/>
+      <c r="Q13" s="4"/>
+    </row>
+    <row r="14" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C14" s="2">
         <v>16</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>15</v>
@@ -1848,7 +2143,7 @@
         <v>15</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>15</v>
@@ -1864,25 +2159,29 @@
         <v>13.370000000000001</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="O14" s="4"/>
-    </row>
-    <row r="15" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+      <c r="O14" s="4">
+        <v>1</v>
+      </c>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="4"/>
+    </row>
+    <row r="15" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C15" s="2">
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>15</v>
@@ -1894,7 +2193,7 @@
         <v>15</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>15</v>
@@ -1910,25 +2209,31 @@
         <v>2.04</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>67</v>
+        <v>175</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="O15" s="4"/>
-    </row>
-    <row r="16" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+      <c r="O15" s="4">
+        <v>1</v>
+      </c>
+      <c r="P15" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q15" s="4"/>
+    </row>
+    <row r="16" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C16" s="2">
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>15</v>
@@ -1940,7 +2245,7 @@
         <v>15</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>15</v>
@@ -1956,25 +2261,31 @@
         <v>8</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>72</v>
+        <v>163</v>
       </c>
       <c r="N16" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="O16" s="4"/>
-    </row>
-    <row r="17" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O16" s="4">
+        <v>1</v>
+      </c>
+      <c r="P16" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q16" s="4"/>
+    </row>
+    <row r="17" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C17" s="2">
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>15</v>
@@ -1986,7 +2297,7 @@
         <v>15</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>15</v>
@@ -2002,25 +2313,29 @@
         <v>1.7999999999999998</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O17" s="4"/>
-    </row>
-    <row r="18" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+      <c r="O17" s="4">
+        <v>1</v>
+      </c>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
+    </row>
+    <row r="18" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C18" s="2">
         <v>24</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>15</v>
@@ -2032,7 +2347,7 @@
         <v>15</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>15</v>
@@ -2048,25 +2363,29 @@
         <v>2.1</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O18" s="4"/>
-    </row>
-    <row r="19" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+      <c r="O18" s="4">
+        <v>1</v>
+      </c>
+      <c r="P18" s="4"/>
+      <c r="Q18" s="4"/>
+    </row>
+    <row r="19" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C19" s="2">
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>15</v>
@@ -2078,7 +2397,7 @@
         <v>15</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>15</v>
@@ -2094,25 +2413,29 @@
         <v>1.2</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O19" s="4"/>
-    </row>
-    <row r="20" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+      <c r="O19" s="4">
+        <v>1</v>
+      </c>
+      <c r="P19" s="4"/>
+      <c r="Q19" s="4"/>
+    </row>
+    <row r="20" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C20" s="2">
         <v>40</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>15</v>
@@ -2124,7 +2447,7 @@
         <v>15</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>15</v>
@@ -2140,25 +2463,29 @@
         <v>6.4</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>83</v>
+        <v>166</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="O20" s="4"/>
-    </row>
-    <row r="21" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O20" s="4">
+        <v>1</v>
+      </c>
+      <c r="P20" s="4"/>
+      <c r="Q20" s="4"/>
+    </row>
+    <row r="21" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C21" s="2">
         <v>16</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>15</v>
@@ -2170,7 +2497,7 @@
         <v>15</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>15</v>
@@ -2186,25 +2513,29 @@
         <v>2.8000000000000003</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="O21" s="4"/>
-    </row>
-    <row r="22" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O21" s="4">
+        <v>1</v>
+      </c>
+      <c r="P21" s="4"/>
+      <c r="Q21" s="4"/>
+    </row>
+    <row r="22" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C22" s="2">
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>89</v>
+        <v>158</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>15</v>
@@ -2216,7 +2547,7 @@
         <v>15</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>15</v>
@@ -2232,25 +2563,31 @@
         <v>4.5</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="N22" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="O22" s="4"/>
-    </row>
-    <row r="23" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O22" s="4">
+        <v>1</v>
+      </c>
+      <c r="P22" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q22" s="4"/>
+    </row>
+    <row r="23" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C23" s="2">
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>15</v>
@@ -2262,7 +2599,7 @@
         <v>15</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>15</v>
@@ -2278,25 +2615,29 @@
         <v>1.5</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="N23" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="O23" s="4"/>
-    </row>
-    <row r="24" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O23" s="4">
+        <v>1</v>
+      </c>
+      <c r="P23" s="4"/>
+      <c r="Q23" s="4"/>
+    </row>
+    <row r="24" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C24" s="2">
         <v>32</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>15</v>
@@ -2308,7 +2649,7 @@
         <v>15</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>15</v>
@@ -2324,25 +2665,29 @@
         <v>1.5</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="N24" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="O24" s="4"/>
-    </row>
-    <row r="25" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O24" s="4">
+        <v>1</v>
+      </c>
+      <c r="P24" s="4"/>
+      <c r="Q24" s="4"/>
+    </row>
+    <row r="25" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C25" s="2">
         <v>16</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>15</v>
@@ -2354,7 +2699,7 @@
         <v>15</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>15</v>
@@ -2370,25 +2715,29 @@
         <v>2</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="O25" s="4"/>
-    </row>
-    <row r="26" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+        <v>93</v>
+      </c>
+      <c r="O25" s="4">
+        <v>1</v>
+      </c>
+      <c r="P25" s="4"/>
+      <c r="Q25" s="4"/>
+    </row>
+    <row r="26" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C26" s="2">
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>15</v>
@@ -2400,7 +2749,7 @@
         <v>15</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>15</v>
@@ -2416,25 +2765,29 @@
         <v>6</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="O26" s="4"/>
-    </row>
-    <row r="27" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O26" s="4">
+        <v>1</v>
+      </c>
+      <c r="P26" s="4"/>
+      <c r="Q26" s="4"/>
+    </row>
+    <row r="27" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C27" s="2">
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>15</v>
@@ -2446,7 +2799,7 @@
         <v>15</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>15</v>
@@ -2462,25 +2815,29 @@
         <v>3.2</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="O27" s="4"/>
-    </row>
-    <row r="28" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O27" s="4">
+        <v>1</v>
+      </c>
+      <c r="P27" s="4"/>
+      <c r="Q27" s="4"/>
+    </row>
+    <row r="28" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C28" s="2">
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>15</v>
@@ -2492,7 +2849,7 @@
         <v>15</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>15</v>
@@ -2508,25 +2865,29 @@
         <v>4</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="O28" s="4"/>
-    </row>
-    <row r="29" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+        <v>93</v>
+      </c>
+      <c r="O28" s="4">
+        <v>1</v>
+      </c>
+      <c r="P28" s="4"/>
+      <c r="Q28" s="4"/>
+    </row>
+    <row r="29" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C29" s="2">
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>15</v>
@@ -2538,7 +2899,7 @@
         <v>15</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>15</v>
@@ -2554,25 +2915,29 @@
         <v>2</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="O29" s="4"/>
-    </row>
-    <row r="30" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+        <v>93</v>
+      </c>
+      <c r="O29" s="4">
+        <v>1</v>
+      </c>
+      <c r="P29" s="4"/>
+      <c r="Q29" s="4"/>
+    </row>
+    <row r="30" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="C30" s="2">
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>15</v>
@@ -2584,7 +2949,7 @@
         <v>15</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>15</v>
@@ -2600,25 +2965,29 @@
         <v>2</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="O30" s="4"/>
-    </row>
-    <row r="31" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+        <v>93</v>
+      </c>
+      <c r="O30" s="4">
+        <v>1</v>
+      </c>
+      <c r="P30" s="4"/>
+      <c r="Q30" s="4"/>
+    </row>
+    <row r="31" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C31" s="2">
         <v>16</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>15</v>
@@ -2630,7 +2999,7 @@
         <v>15</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>15</v>
@@ -2646,25 +3015,29 @@
         <v>4.3999999999999995</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="O31" s="4"/>
-    </row>
-    <row r="32" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+      <c r="O31" s="4">
+        <v>1</v>
+      </c>
+      <c r="P31" s="4"/>
+      <c r="Q31" s="4"/>
+    </row>
+    <row r="32" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C32" s="2">
         <v>16</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>122</v>
+        <v>171</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>15</v>
@@ -2676,7 +3049,7 @@
         <v>15</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>15</v>
@@ -2692,25 +3065,31 @@
         <v>29</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="O32" s="4"/>
-    </row>
-    <row r="33" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+        <v>117</v>
+      </c>
+      <c r="O32" s="4">
+        <v>1</v>
+      </c>
+      <c r="P32" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q32" s="4"/>
+    </row>
+    <row r="33" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C33" s="2">
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>15</v>
@@ -2722,7 +3101,7 @@
         <v>15</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>15</v>
@@ -2738,25 +3117,29 @@
         <v>35.6</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="O33" s="4"/>
-    </row>
-    <row r="34" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+      <c r="O33" s="4">
+        <v>1</v>
+      </c>
+      <c r="P33" s="4"/>
+      <c r="Q33" s="4"/>
+    </row>
+    <row r="34" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C34" s="2">
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>15</v>
@@ -2768,7 +3151,7 @@
         <v>15</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>15</v>
@@ -2784,25 +3167,31 @@
         <v>17.600000000000001</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="N34" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="O34" s="4"/>
-    </row>
-    <row r="35" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O34" s="4">
+        <v>1</v>
+      </c>
+      <c r="P34" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q34" s="4"/>
+    </row>
+    <row r="35" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="C35" s="2">
         <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>134</v>
+        <v>173</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>15</v>
@@ -2814,7 +3203,7 @@
         <v>15</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>15</v>
@@ -2830,25 +3219,31 @@
         <v>20</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="O35" s="4"/>
-    </row>
-    <row r="36" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+        <v>128</v>
+      </c>
+      <c r="O35" s="4">
+        <v>1</v>
+      </c>
+      <c r="P35" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q35" s="4"/>
+    </row>
+    <row r="36" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="C36" s="2">
         <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>15</v>
@@ -2860,7 +3255,7 @@
         <v>15</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>15</v>
@@ -2876,25 +3271,29 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="O36" s="4"/>
-    </row>
-    <row r="37" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+      <c r="O36" s="4">
+        <v>1</v>
+      </c>
+      <c r="P36" s="4"/>
+      <c r="Q36" s="4"/>
+    </row>
+    <row r="37" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="C37" s="2">
         <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>15</v>
@@ -2906,7 +3305,7 @@
         <v>15</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>15</v>
@@ -2922,25 +3321,27 @@
         <v>31.2</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="O37" s="4"/>
-    </row>
-    <row r="38" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P37" s="4"/>
+      <c r="Q37" s="4"/>
+    </row>
+    <row r="38" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="C38" s="2">
         <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>15</v>
@@ -2952,7 +3353,7 @@
         <v>15</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>15</v>
@@ -2968,25 +3369,29 @@
         <v>30.08</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="O38" s="4"/>
-    </row>
-    <row r="39" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+        <v>142</v>
+      </c>
+      <c r="O38" s="4">
+        <v>1</v>
+      </c>
+      <c r="P38" s="4"/>
+      <c r="Q38" s="4"/>
+    </row>
+    <row r="39" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="C39" s="2">
         <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>15</v>
@@ -2998,7 +3403,7 @@
         <v>15</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>15</v>
@@ -3014,25 +3419,29 @@
         <v>28</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="N39" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O39" s="4"/>
-    </row>
-    <row r="40" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O39" s="4">
+        <v>1</v>
+      </c>
+      <c r="P39" s="4"/>
+      <c r="Q39" s="4"/>
+    </row>
+    <row r="40" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="C40" s="2">
         <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>15</v>
@@ -3044,7 +3453,7 @@
         <v>15</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>15</v>
@@ -3060,14 +3469,18 @@
         <v>6.8000000000000007</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="N40" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="O40" s="4"/>
-    </row>
-    <row r="41" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O40" s="4">
+        <v>1</v>
+      </c>
+      <c r="P40" s="4"/>
+      <c r="Q40" s="4"/>
+    </row>
+    <row r="41" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>40</v>
       </c>
@@ -3076,7 +3489,7 @@
       </c>
       <c r="C41" s="2"/>
       <c r="D41" s="2" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>15</v>
@@ -3109,16 +3522,20 @@
       <c r="N41" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O41" s="4"/>
-    </row>
-    <row r="42" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O41" s="4">
+        <v>1</v>
+      </c>
+      <c r="P41" s="4"/>
+      <c r="Q41" s="4"/>
+    </row>
+    <row r="42" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>41</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
@@ -3137,18 +3554,22 @@
       </c>
       <c r="M42" s="2"/>
       <c r="N42" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="O42" s="4"/>
-    </row>
-    <row r="43" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+      <c r="O42" s="4">
+        <v>1</v>
+      </c>
+      <c r="P42" s="4"/>
+      <c r="Q42" s="4"/>
+    </row>
+    <row r="43" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>42</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
@@ -3167,11 +3588,13 @@
       </c>
       <c r="M43" s="2"/>
       <c r="N43" s="2" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="O43" s="4"/>
-    </row>
-    <row r="44" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P43" s="4"/>
+      <c r="Q43" s="4"/>
+    </row>
+    <row r="44" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
@@ -3182,7 +3605,7 @@
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="L44" s="1">
         <f>SUM(L2:L43)</f>
@@ -3191,6 +3614,8 @@
       <c r="M44" s="1"/>
       <c r="N44" s="1"/>
       <c r="O44" s="4"/>
+      <c r="P44" s="4"/>
+      <c r="Q44" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/my/selfHardWarePCB/MotorDriver/采购元件/采购订单.xlsx
+++ b/my/selfHardWarePCB/MotorDriver/采购元件/采购订单.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\project\roboticArm\my\selfHardWarePCB\MotorDriver\采购元件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F53F56CD-72B5-4D68-BD03-80F553C784C4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{669D7D83-285E-4143-8042-521930C72443}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -726,7 +726,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -753,14 +753,6 @@
       <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="20"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2016,7 +2008,9 @@
       <c r="N11" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="O11" s="6"/>
+      <c r="O11" s="6">
+        <v>1</v>
+      </c>
       <c r="P11" s="6"/>
       <c r="Q11" s="4" t="s">
         <v>169</v>
@@ -3326,7 +3320,9 @@
       <c r="N37" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="O37" s="4"/>
+      <c r="O37" s="4">
+        <v>1</v>
+      </c>
       <c r="P37" s="4"/>
       <c r="Q37" s="4"/>
     </row>
